--- a/public/templates/StockNBook_Inventory_Import_Template.xlsx
+++ b/public/templates/StockNBook_Inventory_Import_Template.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ellise James Tamayo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f1876bbe4d985e3c/文档/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63C73D4-46F2-4817-9B98-C20C696FF532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B3DBBD6-67FA-475E-88BA-58BCE400547B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{776D75E4-2865-457B-B649-D74B21262DAF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{776D75E4-2865-457B-B649-D74B21262DAF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Format" sheetId="2" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="1" r:id="rId2"/>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Format" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -270,15 +270,14 @@
     <t>Sales</t>
   </si>
   <si>
-    <t>Expiration Date (Optional)</t>
+    <t>Expiraion Date (Optional)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="8" formatCode="&quot;₱&quot;#,##0.00;[Red]\-&quot;₱&quot;#,##0.00"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\₱#,##0.00"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
@@ -367,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -376,6 +375,12 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -388,15 +393,6 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,247 +707,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BE9EB9-E090-4231-B962-2A2A068DF216}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
-    <col min="2" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.33203125" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BECF1AD2-3C32-4F99-ADC8-C236CFF10B0A}">
   <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -966,18 +721,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -994,124 +749,124 @@
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1127,4 +882,245 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BE9EB9-E090-4231-B962-2A2A068DF216}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="33.33203125" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>